--- a/data/trans_orig/IP16B98-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B98-Provincia-trans_orig.xlsx
@@ -3132,7 +3132,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32418</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
